--- a/docs/MindX 6.0.RC1 通信矩阵.xlsx
+++ b/docs/MindX 6.0.RC1 通信矩阵.xlsx
@@ -4,18 +4,16 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17775" tabRatio="530" activeTab="1"/>
+    <workbookView windowHeight="17775" tabRatio="530"/>
   </bookViews>
   <sheets>
-    <sheet name="封面" sheetId="5" r:id="rId1"/>
-    <sheet name="MindX SDK" sheetId="9" r:id="rId2"/>
+    <sheet name="MindX SDK" sheetId="9" r:id="rId1"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId7"/>
+    <externalReference r:id="rId6"/>
   </externalReferences>
   <definedNames>
     <definedName name="_FTN1">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">封面!$A$1:$E$23</definedName>
     <definedName name="unitENG">[1]数据固化!$AB$4:$AB$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -452,190 +450,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="66">
-  <si>
-    <t>资料编码</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>MindX 5.0.RC2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="24"/>
-        <color rgb="FF000000"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>通信矩阵</t>
-    </r>
-  </si>
-  <si>
-    <t>文档版本</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>发布日期</t>
-  </si>
-  <si>
-    <t>华为技术有限公司</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>版权所有</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> © </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>华为技术有限公司</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 2021</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>。</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>保留一切权利。</t>
-    </r>
-  </si>
-  <si>
-    <t>非经本公司书面许可，任何单位和个人不得擅自摘抄、复制本文档内容的部分或全部，并不得以任何形式传播。</t>
-  </si>
-  <si>
-    <t>商标声明</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     和其他华为商标均为华为技术有限公司的商标。</t>
-  </si>
-  <si>
-    <t>本文档提及的其他所有商标或注册商标，由各自的所有人拥有。</t>
-  </si>
-  <si>
-    <t>注意</t>
-  </si>
-  <si>
-    <t>您购买的产品、服务或特性等应受华为公司商业合同和条款的约束，本文档中描述的全部或部分产品、服务或特性可能不在您的购买或使用范围之内。除非合同另有约定，华为公司对本文档内容不做任何明示或暗示的声明或保证。</t>
-  </si>
-  <si>
-    <t>由于产品版本升级或其他原因，本文档内容会不定期进行更新。除非另有约定，本文档仅作为使用指导，本文档中的所有陈述、信息和建议不构成任何明示或暗示的担保。</t>
-  </si>
-  <si>
-    <t>地址：</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>深圳市龙岗区坂田华为总部办公楼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">     </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>邮编：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>518129</t>
-    </r>
-  </si>
-  <si>
-    <t>网址：</t>
-  </si>
-  <si>
-    <t>http://www.huawei.com</t>
-  </si>
-  <si>
-    <t>客户服务邮箱：</t>
-  </si>
-  <si>
-    <t>support@huawei.com</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="46">
   <si>
     <t>源设备</t>
   </si>
@@ -785,14 +600,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="48">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <name val="宋体"/>
@@ -827,105 +641,6 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="12"/>
-      <color indexed="12"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color indexed="12"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF0000FF"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="12"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10.5"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="8"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color indexed="12"/>
-      <name val="Arial"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -1071,22 +786,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="12"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="24"/>
-      <color rgb="FF000000"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1112,7 +813,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1134,12 +835,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="65"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1484,163 +1179,163 @@
     <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1667,87 +1362,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="59">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="59" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="59" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="59" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="59" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="59" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="59" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="59" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="5" borderId="0" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="5" borderId="0" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="59" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="59" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="59" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="59" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="59" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="59" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="56" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="59" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="59" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="59" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="59" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="59" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="6" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="59" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="60">
@@ -1819,151 +1433,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 9" descr="image001.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1" cstate="print"/>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="920115"/>
-          <a:ext cx="6591300" cy="3298190"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>3627905</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>754717</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>797859</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>1622613</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2" descr="C:\Users\f00250756.CHINA\Desktop\HW_POS_RBG_Vertical-150ppi.jpg"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5504180" y="6862445"/>
-          <a:ext cx="1294130" cy="868045"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>35859</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>188258</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>313765</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>242048</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="图片 3" descr="C:\Users\f00250756.CHINA\Desktop\HW_POS_RBG_Vertical-150ppi.jpg"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId3" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="35560" y="9151620"/>
-          <a:ext cx="278130" cy="254000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2284,340 +1753,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J37"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="11.25" style="9" customWidth="1"/>
-    <col min="2" max="2" width="13.375" style="9" customWidth="1"/>
-    <col min="3" max="3" width="54.125" style="9" customWidth="1"/>
-    <col min="4" max="4" width="13.375" style="9" customWidth="1"/>
-    <col min="5" max="5" width="11.25" style="9" customWidth="1"/>
-    <col min="6" max="41" width="10.625" style="9" customWidth="1"/>
-    <col min="42" max="16384" width="0" style="9" hidden="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="35.1" customHeight="1" spans="1:5">
-      <c r="A1" s="10"/>
-      <c r="B1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="12"/>
-    </row>
-    <row r="2" ht="37.35" customHeight="1" spans="1:5">
-      <c r="A2" s="10"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="12"/>
-    </row>
-    <row r="3" ht="259.7" customHeight="1" spans="1:5">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="12"/>
-    </row>
-    <row r="4" ht="111.6" customHeight="1" spans="1:5">
-      <c r="A4" s="10"/>
-      <c r="B4" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="12"/>
-    </row>
-    <row r="5" ht="18.6" customHeight="1" spans="1:5">
-      <c r="A5" s="10"/>
-      <c r="B5" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="12"/>
-    </row>
-    <row r="6" ht="18.6" customHeight="1" spans="1:5">
-      <c r="A6" s="10"/>
-      <c r="B6" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="19">
-        <v>45107</v>
-      </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="12"/>
-    </row>
-    <row r="7" ht="130.35" customHeight="1" spans="1:5">
-      <c r="A7" s="10"/>
-      <c r="B7" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="12"/>
-    </row>
-    <row r="8" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A8" s="10"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-    </row>
-    <row r="9" ht="33" customHeight="1" spans="1:10">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="12"/>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="10" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A10" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-    </row>
-    <row r="11" ht="33" customHeight="1" spans="1:10">
-      <c r="A11" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="26"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1" spans="1:10">
-      <c r="A12" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
-    </row>
-    <row r="13" ht="25.7" customHeight="1" spans="1:10">
-      <c r="A13" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
-    </row>
-    <row r="14" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A14" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1" spans="1:10">
-      <c r="A15" s="27"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1" spans="1:10">
-      <c r="A16" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26"/>
-    </row>
-    <row r="17" ht="42" customHeight="1" spans="1:10">
-      <c r="A17" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="35"/>
-    </row>
-    <row r="18" ht="29.25" customHeight="1" spans="1:10">
-      <c r="A18" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="25"/>
-      <c r="J18" s="35"/>
-    </row>
-    <row r="19" ht="15.75" spans="1:10">
-      <c r="A19" s="28"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-    </row>
-    <row r="20" ht="20.25" spans="1:9">
-      <c r="A20" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="31"/>
-    </row>
-    <row r="21" customHeight="1" spans="1:9">
-      <c r="A21" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
-    </row>
-    <row r="22" ht="20.25" customHeight="1" spans="1:9">
-      <c r="A22" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="31"/>
-    </row>
-    <row r="23" ht="28.15" customHeight="1" spans="1:9">
-      <c r="A23" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="C23" s="34"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="31"/>
-    </row>
-    <row r="35" customHeight="1"/>
-    <row r="36" customHeight="1"/>
-    <row r="37" customHeight="1"/>
-  </sheetData>
-  <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
-  <mergeCells count="20">
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="E1:E9"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="B23" r:id="rId2" display="support@huawei.com"/>
-    <hyperlink ref="B22:D22" r:id="rId3" display="http://www.huawei.com"/>
-  </hyperlinks>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.15748031496063" right="0.15748031496063" top="1.5748031496063" bottom="0.15748031496063" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="96" orientation="portrait"/>
-  <headerFooter/>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="8" max="4" man="1"/>
-  </rowBreaks>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:O8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
@@ -2639,378 +1774,378 @@
   <sheetData>
     <row r="1" ht="25.5" spans="1:15">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" ht="93" customHeight="1" spans="1:15">
       <c r="A2" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="68" customHeight="1" spans="1:15">
       <c r="A3" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" ht="51" spans="1:15">
       <c r="A4" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" ht="51" spans="1:15">
       <c r="A5" s="2" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" ht="51" spans="1:15">
       <c r="A6" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="G6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="I6" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" ht="51" spans="1:15">
       <c r="A7" s="2" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="I7" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" ht="54" spans="1:15">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="F8" s="6">
         <v>53</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="J8" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="K8" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="L8" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/docs/MindX 6.0.RC1 通信矩阵.xlsx
+++ b/docs/MindX 6.0.RC1 通信矩阵.xlsx
@@ -1025,7 +1025,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1037,19 +1037,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -1186,7 +1173,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1198,34 +1185,34 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1335,7 +1322,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1345,19 +1332,22 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1847,22 +1837,22 @@
       <c r="I2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="M2" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="N2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="O2" s="9" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1894,22 +1884,22 @@
       <c r="I3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="9" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1941,22 +1931,22 @@
       <c r="I4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="M4" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="N4" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="O4" s="9" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1988,22 +1978,22 @@
       <c r="I5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="L5" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="M5" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="N5" s="8" t="s">
+      <c r="N5" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="O5" s="8" t="s">
+      <c r="O5" s="9" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2035,22 +2025,22 @@
       <c r="I6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="L6" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="M6" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="N6" s="8" t="s">
+      <c r="N6" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="O6" s="8" t="s">
+      <c r="O6" s="9" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2061,7 +2051,7 @@
       <c r="B7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D7" s="2" t="s">
@@ -2082,22 +2072,22 @@
       <c r="I7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L7" s="8" t="s">
+      <c r="L7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="M7" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="N7" s="8" t="s">
+      <c r="N7" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="O7" s="8" t="s">
+      <c r="O7" s="9" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2111,40 +2101,40 @@
       <c r="C8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="7">
         <v>53</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="8" t="s">
         <v>43</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="M8" s="8" t="s">
+      <c r="M8" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="N8" s="8" t="s">
+      <c r="N8" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="O8" s="8" t="s">
+      <c r="O8" s="9" t="s">
         <v>26</v>
       </c>
     </row>
